--- a/artfynd/A 35996-2026 artfynd.xlsx
+++ b/artfynd/A 35996-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136042751</v>
       </c>
       <c r="B2" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136042752</v>
       </c>
       <c r="B3" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136042754</v>
       </c>
       <c r="B4" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136194188</v>
       </c>
       <c r="B5" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35996-2026 artfynd.xlsx
+++ b/artfynd/A 35996-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136042751</v>
       </c>
       <c r="B2" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136042752</v>
       </c>
       <c r="B3" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136042754</v>
       </c>
       <c r="B4" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136194188</v>
       </c>
       <c r="B5" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35996-2026 artfynd.xlsx
+++ b/artfynd/A 35996-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136042751</v>
       </c>
       <c r="B2" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136042752</v>
       </c>
       <c r="B3" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136042754</v>
       </c>
       <c r="B4" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136194188</v>
       </c>
       <c r="B5" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35996-2026 artfynd.xlsx
+++ b/artfynd/A 35996-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136042751</v>
       </c>
       <c r="B2" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136042752</v>
       </c>
       <c r="B3" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136042754</v>
       </c>
       <c r="B4" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136194188</v>
       </c>
       <c r="B5" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35996-2026 artfynd.xlsx
+++ b/artfynd/A 35996-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136042751</v>
       </c>
       <c r="B2" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136042752</v>
       </c>
       <c r="B3" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136042754</v>
       </c>
       <c r="B4" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136194188</v>
       </c>
       <c r="B5" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35996-2026 artfynd.xlsx
+++ b/artfynd/A 35996-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136042751</v>
       </c>
       <c r="B2" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136042752</v>
       </c>
       <c r="B3" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136042754</v>
       </c>
       <c r="B4" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136194188</v>
       </c>
       <c r="B5" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
